--- a/AWS_Azure_Services.xlsx
+++ b/AWS_Azure_Services.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\All_Notes_from_learning\All_Notes_to_Share\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868611E8-E791-403E-B3E5-CAB419994EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365CF3E7-43AC-44DE-871B-7BFE9DA89BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23310" windowHeight="13740" xr2:uid="{C72C36B8-A962-49CC-9265-6A2466A87FEF}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="All_Azure_services" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
